--- a/transactions.xlsx
+++ b/transactions.xlsx
@@ -397,10 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B1"/>
   <cols>
-    <col min="1" max="1" width="18.1640625" customWidth="1"/>
-    <col min="2" max="2" width="18.1640625" customWidth="1"/>
+    <col min="1" max="1" width="22.00390625" customWidth="1"/>
+    <col min="2" max="2" width="22.00390625" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" customWidth="1"/>
     <col min="5" max="5" width="16.6640625" customWidth="1"/>
@@ -435,97 +435,9 @@
         <v>購入価格</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ASML</v>
-      </c>
-      <c r="B2" t="str">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>NVDA</v>
-      </c>
-      <c r="B3" t="str">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>MSFT</v>
-      </c>
-      <c r="B4" t="str">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>SONY</v>
-      </c>
-      <c r="B5" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>7974.T</v>
-      </c>
-      <c r="B6" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>7203.T</v>
-      </c>
-      <c r="B7" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>6971.T</v>
-      </c>
-      <c r="B8" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>6146.T</v>
-      </c>
-      <c r="B9" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>6323.T</v>
-      </c>
-      <c r="B10" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>6383.T</v>
-      </c>
-      <c r="B11" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>6920.T</v>
-      </c>
-      <c r="B12" t="str">
-        <v>20</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B1"/>
   </ignoredErrors>
 </worksheet>
 </file>